--- a/artfynd/A 12796-2024 artfynd.xlsx
+++ b/artfynd/A 12796-2024 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115807405</v>
+        <v>116137463</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stockshultskärr (Stockshultskärr), Sm</t>
+          <t>Stockshultskärr, Stockshultskärr, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585356</v>
+        <v>585284</v>
       </c>
       <c r="R2" t="n">
-        <v>6372188</v>
+        <v>6372269</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,70 +770,69 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115807668</v>
+        <v>116138284</v>
       </c>
       <c r="B3" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stockshultskärr (Stockshultskärr), Sm</t>
+          <t>Stockshult, Stockshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585299</v>
+        <v>585200</v>
       </c>
       <c r="R3" t="n">
-        <v>6372172</v>
+        <v>6372378</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,12 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,27 +886,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115807597</v>
+        <v>116137036</v>
       </c>
       <c r="B4" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +909,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stockshultskärr (Stockshultskärr), Sm</t>
+          <t>Stockshultskärr, Stockshultskärr, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585298</v>
+        <v>585268</v>
       </c>
       <c r="R4" t="n">
-        <v>6372163</v>
+        <v>6372166</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +963,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,27 +993,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115968095</v>
+        <v>115807405</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,37 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stockshult, Sm</t>
+          <t>Stockshultskärr, Stockshultskärr, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585436</v>
+        <v>585356</v>
       </c>
       <c r="R5" t="n">
-        <v>6372223</v>
+        <v>6372188</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,11 +1076,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,49 +1090,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115968094</v>
+        <v>115968095</v>
       </c>
       <c r="B6" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585388</v>
+        <v>585436</v>
       </c>
       <c r="R6" t="n">
-        <v>6372187</v>
+        <v>6372223</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1177,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,15 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116137505</v>
+        <v>116138859</v>
       </c>
       <c r="B7" t="n">
-        <v>104820</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,46 +1215,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stockshultskärr (Stockshultskärr), Sm</t>
+          <t>Stockshult, Stockshult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585285</v>
+        <v>585157</v>
       </c>
       <c r="R7" t="n">
-        <v>6372272</v>
+        <v>6372462</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,7 +1279,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1294,7 +1289,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,15 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116137036</v>
+        <v>115807597</v>
       </c>
       <c r="B8" t="n">
-        <v>90435</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,37 +1327,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stockshultskärr (Stockshultskärr), Sm</t>
+          <t>Stockshultskärr, Stockshultskärr, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585268</v>
+        <v>585298</v>
       </c>
       <c r="R8" t="n">
-        <v>6372166</v>
+        <v>6372163</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,22 +1381,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,65 +1401,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116138801</v>
+        <v>115807668</v>
       </c>
       <c r="B9" t="n">
-        <v>97733</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stockshult (Stockshult), Sm</t>
+          <t>Stockshultskärr, Stockshultskärr, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585160</v>
+        <v>585299</v>
       </c>
       <c r="R9" t="n">
-        <v>6372473</v>
+        <v>6372172</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1503,22 +1483,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,74 +1503,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116137413</v>
+        <v>115968094</v>
       </c>
       <c r="B10" t="n">
-        <v>97733</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stockshultskärr (Stockshultskärr), Sm</t>
+          <t>Stockshult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585282</v>
+        <v>585388</v>
       </c>
       <c r="R10" t="n">
-        <v>6372274</v>
+        <v>6372187</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1624,22 +1580,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,62 +1605,66 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116137463</v>
+        <v>116137413</v>
       </c>
       <c r="B11" t="n">
-        <v>94512</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stockshultskärr (Stockshultskärr), Sm</t>
+          <t>Stockshultskärr, Stockshultskärr, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585284</v>
+        <v>585282</v>
       </c>
       <c r="R11" t="n">
-        <v>6372269</v>
+        <v>6372274</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1741,7 +1696,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1706,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,55 +1733,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116138859</v>
+        <v>116138801</v>
       </c>
       <c r="B12" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stockshult (Stockshult), Sm</t>
+          <t>Stockshult, Stockshult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585157</v>
+        <v>585160</v>
       </c>
       <c r="R12" t="n">
-        <v>6372462</v>
+        <v>6372473</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1858,7 +1803,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,7 +1813,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,15 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116138284</v>
+        <v>116137505</v>
       </c>
       <c r="B13" t="n">
-        <v>94512</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,26 +1851,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1940,17 +1880,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stockshult (Stockshult), Sm</t>
+          <t>Stockshultskärr, Stockshultskärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585200</v>
+        <v>585285</v>
       </c>
       <c r="R13" t="n">
-        <v>6372378</v>
+        <v>6372272</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1979,7 +1919,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,7 +1929,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 12796-2024 artfynd.xlsx
+++ b/artfynd/A 12796-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116137463</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116138284</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116137036</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115807405</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116138859</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115807597</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115807668</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968094</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1730,6 +1780,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116137413</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116138801</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1953,8 +2013,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116137505</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>